--- a/data/trans_camb/P74B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 20,5</t>
+          <t>0,0; 16,98</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,73</t>
+          <t>0,0; 38,89</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-36,04; 29,43</t>
+          <t>-43,69; 29,22</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-51,83; 8,59</t>
+          <t>-53,23; 8,49</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,51; 18,31</t>
+          <t>-2,6; 18,95</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-2,69; 16,88</t>
+          <t>-1,89; 16,93</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 0,99</t>
+          <t>-4,87; 0,83</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,41; 6,92</t>
+          <t>-1,71; 6,6</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>15,95; 36,69</t>
+          <t>16,07; 36,22</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>5,81; 27,2</t>
+          <t>6,48; 27,1</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,01; 13,28</t>
+          <t>3,36; 12,87</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,36; 9,61</t>
+          <t>1,03; 9,01</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-75,17; 1130,49</t>
+          <t>-73,54; 996,88</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>12,32; 2088,72</t>
+          <t>22,35; 2162,47</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-4,93; 1577,4</t>
+          <t>-30,11; 1213,17</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,34; 6,21</t>
+          <t>1,31; 6,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,64; 8,04</t>
+          <t>1,36; 7,49</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,36; 3,06</t>
+          <t>-27,75; 2,44</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,9; 6,93</t>
+          <t>-25,14; 4,91</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,15; 7,6</t>
+          <t>-0,25; 7,11</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>-0,12; 8,09</t>
+          <t>0,3; 8,36</t>
         </is>
       </c>
     </row>
@@ -1029,22 +1029,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-66,46; 21,98</t>
+          <t>-65,42; 15,39</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-62,96; 37,51</t>
+          <t>-64,74; 23,26</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-5,15; 248,38</t>
+          <t>-4,41; 237,05</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-7,43; 268,15</t>
+          <t>-1,17; 253,21</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,31; 4,27</t>
+          <t>-1,22; 4,46</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,02; 6,52</t>
+          <t>-0,33; 6,34</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-41,63; -13,42</t>
+          <t>-42,62; -13,51</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-55,26; -29,05</t>
+          <t>-55,55; -29,42</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,38; 7,11</t>
+          <t>-4,13; 6,77</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,5; 3,16</t>
+          <t>-7,39; 2,43</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-48,88; 412,13</t>
+          <t>-52,31; 425,91</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-18,89; 587,2</t>
+          <t>-38,22; 635,36</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-52,75; -20,03</t>
+          <t>-53,55; -20,82</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,26; -45,99</t>
+          <t>-71,21; -46,87</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-25,06; 58,85</t>
+          <t>-24,18; 50,78</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-41,05; 26,91</t>
+          <t>-40,9; 18,72</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,89; 5,32</t>
+          <t>-4,04; 6,09</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,51; 5,42</t>
+          <t>-4,5; 5,62</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,75; 4,33</t>
+          <t>-8,79; 4,48</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-14,37; 1,33</t>
+          <t>-13,45; 1,51</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-0,77; 11,74</t>
+          <t>-1,18; 11,51</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,05; 8,93</t>
+          <t>-4,56; 7,96</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-44,56; 86,83</t>
+          <t>-39,63; 102,41</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-44,83; 93,02</t>
+          <t>-43,81; 87,97</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,66; 5,22</t>
+          <t>-9,75; 5,36</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-15,89; 1,81</t>
+          <t>-14,96; 1,8</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,08; 34,08</t>
+          <t>-2,95; 32,95</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-9,99; 26,0</t>
+          <t>-10,83; 22,08</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>1,26; 17,54</t>
+          <t>2,43; 17,35</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,42; 15,6</t>
+          <t>1,01; 16,59</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,71; 4,46</t>
+          <t>-3,92; 4,08</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,49; 6,41</t>
+          <t>0,48; 6,82</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,9; 12,31</t>
+          <t>-0,63; 12,81</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,01; 14,14</t>
+          <t>2,02; 14,1</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>2,94; 110,39</t>
+          <t>11,05; 114,8</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>4,71; 101,74</t>
+          <t>3,77; 106,51</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-3,76; 4,76</t>
+          <t>-4,04; 4,33</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,93</t>
+          <t>0,49; 7,43</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,63; 24,64</t>
+          <t>-1,15; 25,62</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,6; 28,02</t>
+          <t>3,58; 27,95</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>4,46; 25,59</t>
+          <t>5,89; 26,95</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>0,2; 19,33</t>
+          <t>1,02; 19,2</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,32; 10,81</t>
+          <t>0,35; 10,49</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-0,93; 9,75</t>
+          <t>-1,59; 9,38</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>2,91; 20,45</t>
+          <t>3,98; 20,98</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>1,22; 17,55</t>
+          <t>2,08; 18,59</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>17,37; 173,01</t>
+          <t>23,68; 194,56</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>0,1; 140,87</t>
+          <t>4,89; 131,91</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,32; 12,2</t>
+          <t>0,35; 11,91</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-0,92; 11,1</t>
+          <t>-1,6; 10,61</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>5,44; 42,87</t>
+          <t>7,06; 44,0</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>2,06; 36,21</t>
+          <t>3,32; 38,67</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,54; 7,45</t>
+          <t>2,67; 7,2</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,71; 7,22</t>
+          <t>2,51; 7,31</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-19,0; -10,59</t>
+          <t>-18,68; -10,18</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-21,3; -12,08</t>
+          <t>-21,04; -12,02</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,78; 7,47</t>
+          <t>1,65; 7,39</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,51; 6,24</t>
+          <t>0,42; 6,33</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>28,74; 115,32</t>
+          <t>30,2; 109,08</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31,16; 111,49</t>
+          <t>31,15; 110,36</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,32; -12,99</t>
+          <t>-22,16; -12,55</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-25,17; -14,89</t>
+          <t>-24,97; -14,84</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,59; 25,72</t>
+          <t>5,23; 25,55</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,58; 21,55</t>
+          <t>1,4; 21,78</t>
         </is>
       </c>
     </row>

--- a/data/trans_camb/P74B-Edad-trans_camb.xlsx
+++ b/data/trans_camb/P74B-Edad-trans_camb.xlsx
@@ -631,32 +631,32 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 16,98</t>
+          <t>0,0; 16,43</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,89</t>
+          <t>0,0; 39,19</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>-43,69; 29,22</t>
+          <t>-37,87; 26,69</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>-53,23; 8,49</t>
+          <t>-57,88; 8,65</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>-2,6; 18,95</t>
+          <t>-2,77; 18,36</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>-1,89; 16,93</t>
+          <t>-2,35; 17,16</t>
         </is>
       </c>
     </row>
@@ -787,32 +787,32 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>-4,87; 0,83</t>
+          <t>-4,64; 0,86</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>-1,71; 6,6</t>
+          <t>-1,11; 6,94</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>16,07; 36,22</t>
+          <t>15,9; 37,37</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>6,48; 27,1</t>
+          <t>6,55; 27,91</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>3,36; 12,87</t>
+          <t>3,46; 13,24</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>1,03; 9,01</t>
+          <t>0,85; 9,59</t>
         </is>
       </c>
     </row>
@@ -868,7 +868,7 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>-73,54; 996,88</t>
+          <t>-56,59; 993,3</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>22,35; 2162,47</t>
+          <t>43,11; 1936,48</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>-30,11; 1213,17</t>
+          <t>-22,17; 1513,25</t>
         </is>
       </c>
     </row>
@@ -943,32 +943,32 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>1,31; 6,5</t>
+          <t>1,69; 6,5</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,36; 7,49</t>
+          <t>1,56; 7,86</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>-27,75; 2,44</t>
+          <t>-29,84; 1,45</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>-25,14; 4,91</t>
+          <t>-27,5; 3,0</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>-0,25; 7,11</t>
+          <t>-0,25; 7,3</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>0,3; 8,36</t>
+          <t>0,34; 8,35</t>
         </is>
       </c>
     </row>
@@ -1029,22 +1029,22 @@
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>-65,42; 15,39</t>
+          <t>-69,18; 8,51</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>-64,74; 23,26</t>
+          <t>-63,89; 19,33</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>-4,41; 237,05</t>
+          <t>-6,85; 223,64</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>-1,17; 253,21</t>
+          <t>0,95; 249,46</t>
         </is>
       </c>
     </row>
@@ -1099,32 +1099,32 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>-1,22; 4,46</t>
+          <t>-1,37; 4,55</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>-0,33; 6,34</t>
+          <t>-0,11; 6,42</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>-42,62; -13,51</t>
+          <t>-41,74; -13,19</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>-55,55; -29,42</t>
+          <t>-55,86; -29,25</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>-4,13; 6,77</t>
+          <t>-4,38; 7,1</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>-7,39; 2,43</t>
+          <t>-8,11; 2,59</t>
         </is>
       </c>
     </row>
@@ -1175,32 +1175,32 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
-          <t>-52,31; 425,91</t>
+          <t>-51,22; 402,12</t>
         </is>
       </c>
       <c r="D19" s="2" t="inlineStr">
         <is>
-          <t>-38,22; 635,36</t>
+          <t>-18,4; 612,32</t>
         </is>
       </c>
       <c r="E19" s="2" t="inlineStr">
         <is>
-          <t>-53,55; -20,82</t>
+          <t>-52,34; -20,57</t>
         </is>
       </c>
       <c r="F19" s="2" t="inlineStr">
         <is>
-          <t>-71,21; -46,87</t>
+          <t>-72,19; -46,03</t>
         </is>
       </c>
       <c r="G19" s="2" t="inlineStr">
         <is>
-          <t>-24,18; 50,78</t>
+          <t>-23,23; 55,63</t>
         </is>
       </c>
       <c r="H19" s="2" t="inlineStr">
         <is>
-          <t>-40,9; 18,72</t>
+          <t>-43,35; 20,82</t>
         </is>
       </c>
     </row>
@@ -1255,32 +1255,32 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 6,09</t>
+          <t>-3,92; 5,88</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>-4,5; 5,62</t>
+          <t>-4,78; 5,4</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>-8,79; 4,48</t>
+          <t>-9,58; 4,95</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>-13,45; 1,51</t>
+          <t>-14,41; 1,24</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>-1,18; 11,51</t>
+          <t>-1,42; 11,26</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>-4,56; 7,96</t>
+          <t>-4,05; 8,53</t>
         </is>
       </c>
     </row>
@@ -1331,32 +1331,32 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
-          <t>-39,63; 102,41</t>
+          <t>-39,4; 100,52</t>
         </is>
       </c>
       <c r="D23" s="2" t="inlineStr">
         <is>
-          <t>-43,81; 87,97</t>
+          <t>-45,74; 94,14</t>
         </is>
       </c>
       <c r="E23" s="2" t="inlineStr">
         <is>
-          <t>-9,75; 5,36</t>
+          <t>-10,5; 5,82</t>
         </is>
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>-14,96; 1,8</t>
+          <t>-15,99; 1,5</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
         <is>
-          <t>-2,95; 32,95</t>
+          <t>-3,31; 31,68</t>
         </is>
       </c>
       <c r="H23" s="2" t="inlineStr">
         <is>
-          <t>-10,83; 22,08</t>
+          <t>-10,21; 24,08</t>
         </is>
       </c>
     </row>
@@ -1411,32 +1411,32 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
-          <t>2,43; 17,35</t>
+          <t>2,18; 17,72</t>
         </is>
       </c>
       <c r="D25" s="2" t="inlineStr">
         <is>
-          <t>1,01; 16,59</t>
+          <t>1,47; 16,01</t>
         </is>
       </c>
       <c r="E25" s="2" t="inlineStr">
         <is>
-          <t>-3,92; 4,08</t>
+          <t>-3,25; 4,6</t>
         </is>
       </c>
       <c r="F25" s="2" t="inlineStr">
         <is>
-          <t>0,48; 6,82</t>
+          <t>0,52; 6,54</t>
         </is>
       </c>
       <c r="G25" s="2" t="inlineStr">
         <is>
-          <t>-0,63; 12,81</t>
+          <t>-0,66; 11,64</t>
         </is>
       </c>
       <c r="H25" s="2" t="inlineStr">
         <is>
-          <t>2,02; 14,1</t>
+          <t>2,31; 14,04</t>
         </is>
       </c>
     </row>
@@ -1487,32 +1487,32 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
-          <t>11,05; 114,8</t>
+          <t>7,75; 113,66</t>
         </is>
       </c>
       <c r="D27" s="2" t="inlineStr">
         <is>
-          <t>3,77; 106,51</t>
+          <t>6,76; 105,47</t>
         </is>
       </c>
       <c r="E27" s="2" t="inlineStr">
         <is>
-          <t>-4,04; 4,33</t>
+          <t>-3,35; 4,88</t>
         </is>
       </c>
       <c r="F27" s="2" t="inlineStr">
         <is>
-          <t>0,49; 7,43</t>
+          <t>0,53; 7,06</t>
         </is>
       </c>
       <c r="G27" s="2" t="inlineStr">
         <is>
-          <t>-1,15; 25,62</t>
+          <t>-1,03; 23,12</t>
         </is>
       </c>
       <c r="H27" s="2" t="inlineStr">
         <is>
-          <t>3,58; 27,95</t>
+          <t>3,87; 28,01</t>
         </is>
       </c>
     </row>
@@ -1567,32 +1567,32 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
-          <t>5,89; 26,95</t>
+          <t>5,87; 26,9</t>
         </is>
       </c>
       <c r="D29" s="2" t="inlineStr">
         <is>
-          <t>1,02; 19,2</t>
+          <t>-0,58; 19,4</t>
         </is>
       </c>
       <c r="E29" s="2" t="inlineStr">
         <is>
-          <t>0,35; 10,49</t>
+          <t>0,29; 9,84</t>
         </is>
       </c>
       <c r="F29" s="2" t="inlineStr">
         <is>
-          <t>-1,59; 9,38</t>
+          <t>-1,35; 9,48</t>
         </is>
       </c>
       <c r="G29" s="2" t="inlineStr">
         <is>
-          <t>3,98; 20,98</t>
+          <t>3,68; 20,7</t>
         </is>
       </c>
       <c r="H29" s="2" t="inlineStr">
         <is>
-          <t>2,08; 18,59</t>
+          <t>1,32; 17,31</t>
         </is>
       </c>
     </row>
@@ -1643,32 +1643,32 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
-          <t>23,68; 194,56</t>
+          <t>22,61; 189,65</t>
         </is>
       </c>
       <c r="D31" s="2" t="inlineStr">
         <is>
-          <t>4,89; 131,91</t>
+          <t>-2,5; 142,5</t>
         </is>
       </c>
       <c r="E31" s="2" t="inlineStr">
         <is>
-          <t>0,35; 11,91</t>
+          <t>0,3; 10,96</t>
         </is>
       </c>
       <c r="F31" s="2" t="inlineStr">
         <is>
-          <t>-1,6; 10,61</t>
+          <t>-1,28; 11,08</t>
         </is>
       </c>
       <c r="G31" s="2" t="inlineStr">
         <is>
-          <t>7,06; 44,0</t>
+          <t>6,33; 43,45</t>
         </is>
       </c>
       <c r="H31" s="2" t="inlineStr">
         <is>
-          <t>3,32; 38,67</t>
+          <t>2,26; 35,97</t>
         </is>
       </c>
     </row>
@@ -1723,32 +1723,32 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
-          <t>2,67; 7,2</t>
+          <t>2,53; 7,36</t>
         </is>
       </c>
       <c r="D33" s="2" t="inlineStr">
         <is>
-          <t>2,51; 7,31</t>
+          <t>2,71; 7,44</t>
         </is>
       </c>
       <c r="E33" s="2" t="inlineStr">
         <is>
-          <t>-18,68; -10,18</t>
+          <t>-19,22; -10,15</t>
         </is>
       </c>
       <c r="F33" s="2" t="inlineStr">
         <is>
-          <t>-21,04; -12,02</t>
+          <t>-21,07; -11,76</t>
         </is>
       </c>
       <c r="G33" s="2" t="inlineStr">
         <is>
-          <t>1,65; 7,39</t>
+          <t>1,59; 7,31</t>
         </is>
       </c>
       <c r="H33" s="2" t="inlineStr">
         <is>
-          <t>0,42; 6,33</t>
+          <t>0,49; 6,06</t>
         </is>
       </c>
     </row>
@@ -1799,32 +1799,32 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
-          <t>30,2; 109,08</t>
+          <t>29,53; 110,76</t>
         </is>
       </c>
       <c r="D35" s="2" t="inlineStr">
         <is>
-          <t>31,15; 110,36</t>
+          <t>30,53; 111,31</t>
         </is>
       </c>
       <c r="E35" s="2" t="inlineStr">
         <is>
-          <t>-22,16; -12,55</t>
+          <t>-22,67; -12,58</t>
         </is>
       </c>
       <c r="F35" s="2" t="inlineStr">
         <is>
-          <t>-24,97; -14,84</t>
+          <t>-24,95; -14,62</t>
         </is>
       </c>
       <c r="G35" s="2" t="inlineStr">
         <is>
-          <t>5,23; 25,55</t>
+          <t>4,97; 25,24</t>
         </is>
       </c>
       <c r="H35" s="2" t="inlineStr">
         <is>
-          <t>1,4; 21,78</t>
+          <t>1,68; 21,29</t>
         </is>
       </c>
     </row>
